--- a/TPR.xlsx
+++ b/TPR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC385A01-3CD8-448A-B635-8BFC23DBD49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E5EB0F-5AB5-4C4C-B338-F477D9917B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{FE2400EE-DFF5-46AE-8520-2B6C3CEB7AD1}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{FE2400EE-DFF5-46AE-8520-2B6C3CEB7AD1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="66">
   <si>
     <t>Tapestry</t>
   </si>
@@ -251,6 +251,9 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>FY26</t>
+  </si>
 </sst>
 </file>
 
@@ -262,13 +265,19 @@
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="167" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -345,44 +354,44 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -753,7 +762,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="2">
-        <v>134.28</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -761,10 +770,10 @@
         <v>5</v>
       </c>
       <c r="J3" s="3">
-        <v>202.044714</v>
+        <v>199.39167800000001</v>
       </c>
-      <c r="K3" s="20" t="s">
-        <v>63</v>
+      <c r="K3" s="21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -776,7 +785,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>27130.56419592</v>
+        <v>25920.918140000002</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -787,11 +796,11 @@
         <v>7</v>
       </c>
       <c r="J5" s="3">
-        <f>1046.5+0.0221</f>
-        <v>1046.5220999999999</v>
+        <f>974.7+177.3</f>
+        <v>1152</v>
       </c>
-      <c r="K5" s="20" t="s">
-        <v>63</v>
+      <c r="K5" s="21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -799,10 +808,11 @@
         <v>8</v>
       </c>
       <c r="J6" s="3">
-        <v>2377.1</v>
+        <f>0+2379</f>
+        <v>2379</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>63</v>
+      <c r="K6" s="21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -814,7 +824,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>28461.14209592</v>
+        <v>27147.918140000002</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -934,6 +944,9 @@
       <c r="V2" s="4" t="s">
         <v>56</v>
       </c>
+      <c r="W2" s="21" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="3" spans="1:163" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -964,6 +977,9 @@
       </c>
       <c r="V3" s="10">
         <v>931</v>
+      </c>
+      <c r="W3" s="2">
+        <v>973</v>
       </c>
     </row>
     <row r="4" spans="1:163" x14ac:dyDescent="0.2">
@@ -996,6 +1012,9 @@
       <c r="V4" s="10">
         <v>360</v>
       </c>
+      <c r="W4" s="2">
+        <v>326</v>
+      </c>
     </row>
     <row r="5" spans="1:163" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -1026,6 +1045,9 @@
       </c>
       <c r="V5" s="10">
         <v>80</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:163" x14ac:dyDescent="0.2">
@@ -1058,6 +1080,10 @@
       <c r="V6" s="10">
         <v>541</v>
       </c>
+      <c r="W6" s="2">
+        <f>336+178</f>
+        <v>514</v>
+      </c>
     </row>
     <row r="7" spans="1:163" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
@@ -1088,6 +1114,10 @@
       </c>
       <c r="V7" s="10">
         <v>830</v>
+      </c>
+      <c r="W7" s="2">
+        <f>637+148</f>
+        <v>785</v>
       </c>
     </row>
     <row r="8" spans="1:163" x14ac:dyDescent="0.2">
@@ -1134,6 +1164,10 @@
       <c r="V8" s="12">
         <f>+V6+V7</f>
         <v>1371</v>
+      </c>
+      <c r="W8" s="12">
+        <f>+W6+W7</f>
+        <v>1299</v>
       </c>
     </row>
     <row r="9" spans="1:163" x14ac:dyDescent="0.2">
@@ -1189,7 +1223,10 @@
       <c r="M10" s="13">
         <v>1701</v>
       </c>
-      <c r="N10" s="13"/>
+      <c r="N10" s="13">
+        <f>+W10-SUM(K10:M10)</f>
+        <v>1641.5</v>
+      </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
@@ -1204,7 +1241,9 @@
       <c r="V10" s="3">
         <v>5598.5</v>
       </c>
-      <c r="W10" s="3"/>
+      <c r="W10" s="3">
+        <v>6914.7</v>
+      </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -1385,7 +1424,10 @@
       <c r="M11" s="13">
         <v>219.6</v>
       </c>
-      <c r="N11" s="13"/>
+      <c r="N11" s="13">
+        <f>+W11-SUM(K11:M11)</f>
+        <v>235.10000000000002</v>
+      </c>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
@@ -1400,7 +1442,9 @@
       <c r="V11" s="3">
         <v>1197.0999999999999</v>
       </c>
-      <c r="W11" s="3"/>
+      <c r="W11" s="3">
+        <v>1074.9000000000001</v>
+      </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
@@ -1578,10 +1622,13 @@
       <c r="L12" s="13">
         <v>0</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="20">
         <v>0</v>
       </c>
-      <c r="N12" s="13"/>
+      <c r="N12" s="13">
+        <f>+W12-SUM(K12:M12)</f>
+        <v>0</v>
+      </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -1596,7 +1643,9 @@
       <c r="V12" s="3">
         <v>215.1</v>
       </c>
-      <c r="W12" s="3"/>
+      <c r="W12" s="3">
+        <v>14.6</v>
+      </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -1777,7 +1826,10 @@
       <c r="M13" s="14">
         <v>1920.6</v>
       </c>
-      <c r="N13" s="14"/>
+      <c r="N13" s="14">
+        <f>+W13-SUM(K13:M13)</f>
+        <v>1876.5999999999995</v>
+      </c>
       <c r="O13" s="3"/>
       <c r="P13" s="15"/>
       <c r="Q13" s="15"/>
@@ -1792,7 +1844,9 @@
       <c r="V13" s="15">
         <v>7010.7</v>
       </c>
-      <c r="W13" s="3"/>
+      <c r="W13" s="15">
+        <v>8004.2</v>
+      </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -1973,7 +2027,10 @@
       <c r="M14" s="13">
         <v>444.1</v>
       </c>
-      <c r="N14" s="13"/>
+      <c r="N14" s="13">
+        <f>+W14-SUM(K14:M14)</f>
+        <v>313</v>
+      </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
@@ -1988,7 +2045,9 @@
       <c r="V14" s="3">
         <v>1721.8</v>
       </c>
-      <c r="W14" s="3"/>
+      <c r="W14" s="3">
+        <v>1775.2</v>
+      </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
@@ -2155,7 +2214,7 @@
         <v>1134.9000000000001</v>
       </c>
       <c r="H15" s="13">
-        <f t="shared" ref="H15:V15" si="4">+H13-H14</f>
+        <f t="shared" ref="H15:W15" si="4">+H13-H14</f>
         <v>1633.1000000000001</v>
       </c>
       <c r="I15" s="13">
@@ -2178,7 +2237,10 @@
         <f t="shared" si="4"/>
         <v>1476.5</v>
       </c>
-      <c r="N15" s="13"/>
+      <c r="N15" s="13">
+        <f t="shared" si="4"/>
+        <v>1563.5999999999995</v>
+      </c>
       <c r="O15" s="3"/>
       <c r="P15" s="13">
         <f t="shared" si="4"/>
@@ -2208,7 +2270,10 @@
         <f t="shared" si="4"/>
         <v>5288.9</v>
       </c>
-      <c r="W15" s="3"/>
+      <c r="W15" s="13">
+        <f t="shared" si="4"/>
+        <v>6229</v>
+      </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
@@ -2389,7 +2454,10 @@
       <c r="M16" s="13">
         <v>1049</v>
       </c>
-      <c r="N16" s="13"/>
+      <c r="N16" s="13">
+        <f>+W16-SUM(K16:M16)</f>
+        <v>1121.3000000000002</v>
+      </c>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
@@ -2405,7 +2473,9 @@
         <f>4019.1+854.8</f>
         <v>4873.8999999999996</v>
       </c>
-      <c r="W16" s="3"/>
+      <c r="W16" s="3">
+        <v>4314.6000000000004</v>
+      </c>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
@@ -2572,7 +2642,7 @@
         <v>252.00000000000011</v>
       </c>
       <c r="H17" s="13">
-        <f t="shared" ref="H17:V17" si="6">+H15-H16</f>
+        <f t="shared" ref="H17:W17" si="6">+H15-H16</f>
         <v>492.80000000000018</v>
       </c>
       <c r="I17" s="13">
@@ -2595,7 +2665,10 @@
         <f t="shared" si="6"/>
         <v>427.5</v>
       </c>
-      <c r="N17" s="13"/>
+      <c r="N17" s="13">
+        <f t="shared" si="6"/>
+        <v>442.29999999999927</v>
+      </c>
       <c r="O17" s="3"/>
       <c r="P17" s="13">
         <f t="shared" si="6"/>
@@ -2625,7 +2698,10 @@
         <f t="shared" si="6"/>
         <v>415</v>
       </c>
-      <c r="W17" s="3"/>
+      <c r="W17" s="13">
+        <f t="shared" si="6"/>
+        <v>1914.3999999999996</v>
+      </c>
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
@@ -2807,7 +2883,10 @@
       <c r="M18" s="13">
         <v>13.1</v>
       </c>
-      <c r="N18" s="13"/>
+      <c r="N18" s="13">
+        <f>+W18-SUM(K18:M18)</f>
+        <v>11.900000000000006</v>
+      </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
@@ -2823,7 +2902,9 @@
         <f>85.4+120.1</f>
         <v>205.5</v>
       </c>
-      <c r="W18" s="3"/>
+      <c r="W18" s="3">
+        <v>55.2</v>
+      </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
@@ -3004,7 +3085,10 @@
       <c r="M19" s="13">
         <v>-1.6</v>
       </c>
-      <c r="N19" s="13"/>
+      <c r="N19" s="13">
+        <f>+W19-SUM(K19:M19)</f>
+        <v>1.6</v>
+      </c>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
@@ -3019,7 +3103,9 @@
       <c r="V19" s="3">
         <v>-6.6</v>
       </c>
-      <c r="W19" s="3"/>
+      <c r="W19" s="3">
+        <v>-1.4</v>
+      </c>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
@@ -3186,7 +3272,7 @@
         <v>225.7000000000001</v>
       </c>
       <c r="H20" s="13">
-        <f t="shared" ref="H20:V20" si="8">+H17-SUM(H18:H19)</f>
+        <f t="shared" ref="H20:W20" si="8">+H17-SUM(H18:H19)</f>
         <v>345.30000000000018</v>
       </c>
       <c r="I20" s="13">
@@ -3209,7 +3295,10 @@
         <f t="shared" si="8"/>
         <v>416</v>
       </c>
-      <c r="N20" s="13"/>
+      <c r="N20" s="13">
+        <f t="shared" si="8"/>
+        <v>428.79999999999927</v>
+      </c>
       <c r="O20" s="3"/>
       <c r="P20" s="13">
         <f t="shared" si="8"/>
@@ -3239,7 +3328,10 @@
         <f t="shared" si="8"/>
         <v>216.1</v>
       </c>
-      <c r="W20" s="3"/>
+      <c r="W20" s="13">
+        <f t="shared" si="8"/>
+        <v>1860.5999999999997</v>
+      </c>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
@@ -3420,7 +3512,10 @@
       <c r="M21" s="13">
         <v>72.2</v>
       </c>
-      <c r="N21" s="13"/>
+      <c r="N21" s="13">
+        <f>+W21-SUM(K21:M21)</f>
+        <v>80.999999999999943</v>
+      </c>
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
@@ -3435,7 +3530,9 @@
       <c r="V21" s="3">
         <v>32.9</v>
       </c>
-      <c r="W21" s="3"/>
+      <c r="W21" s="3">
+        <v>332.9</v>
+      </c>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
@@ -3602,7 +3699,7 @@
         <v>186.60000000000011</v>
       </c>
       <c r="H22" s="13">
-        <f t="shared" ref="H22:V22" si="10">+H20-H21</f>
+        <f t="shared" ref="H22:W22" si="10">+H20-H21</f>
         <v>310.4000000000002</v>
       </c>
       <c r="I22" s="13">
@@ -3625,7 +3722,10 @@
         <f t="shared" si="10"/>
         <v>343.8</v>
       </c>
-      <c r="N22" s="13"/>
+      <c r="N22" s="13">
+        <f t="shared" si="10"/>
+        <v>347.79999999999933</v>
+      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="13">
         <f t="shared" si="10"/>
@@ -3655,7 +3755,10 @@
         <f t="shared" si="10"/>
         <v>183.2</v>
       </c>
-      <c r="W22" s="3"/>
+      <c r="W22" s="13">
+        <f t="shared" si="10"/>
+        <v>1527.6999999999998</v>
+      </c>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
@@ -3985,7 +4088,7 @@
         <v>0.80604751619870452</v>
       </c>
       <c r="H24" s="19">
-        <f t="shared" ref="H24:M24" si="12">+H22/H25</f>
+        <f t="shared" ref="H24:L24" si="12">+H22/H25</f>
         <v>1.4115507048658491</v>
       </c>
       <c r="I24" s="19">
@@ -4005,10 +4108,13 @@
         <v>2.7501224889759932</v>
       </c>
       <c r="M24" s="19">
-        <f t="shared" si="12"/>
+        <f>+M22/M25</f>
         <v>1.6977777777777778</v>
       </c>
-      <c r="N24" s="19"/>
+      <c r="N24" s="19">
+        <f>+N22/N25</f>
+        <v>1.7175308641975275</v>
+      </c>
       <c r="O24" s="19"/>
       <c r="P24" s="19" t="e">
         <f t="shared" ref="P24:U24" si="13">+P22/P25</f>
@@ -4038,7 +4144,10 @@
         <f>+V22/V25</f>
         <v>0.84501845018450172</v>
       </c>
-      <c r="W24" s="19"/>
+      <c r="W24" s="19">
+        <f>+W22/W25</f>
+        <v>7.4887254901960771</v>
+      </c>
       <c r="X24" s="19"/>
       <c r="Y24" s="19"/>
       <c r="Z24" s="19"/>
@@ -4219,7 +4328,9 @@
       <c r="M25" s="3">
         <v>202.5</v>
       </c>
-      <c r="N25" s="3"/>
+      <c r="N25" s="3">
+        <v>202.5</v>
+      </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
@@ -4234,7 +4345,9 @@
       <c r="V25" s="3">
         <v>216.8</v>
       </c>
-      <c r="W25" s="3"/>
+      <c r="W25" s="3">
+        <v>204</v>
+      </c>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
@@ -4581,7 +4694,10 @@
         <f>+V8/U8-1</f>
         <v>-2.2111269614835893E-2</v>
       </c>
-      <c r="W27" s="3"/>
+      <c r="W27" s="16">
+        <f>+W8/V8-1</f>
+        <v>-5.2516411378555783E-2</v>
+      </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
@@ -4759,7 +4875,10 @@
         <f>+M10/I10-1</f>
         <v>0.31503672207189792</v>
       </c>
-      <c r="N28" s="16"/>
+      <c r="N28" s="16">
+        <f>+N10/J10-1</f>
+        <v>0.15184899305311883</v>
+      </c>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="16" t="e">
@@ -4786,7 +4905,10 @@
         <f>+V10/U10-1</f>
         <v>9.8757678645025715E-2</v>
       </c>
-      <c r="W28" s="3"/>
+      <c r="W28" s="16">
+        <f>+W10/V10-1</f>
+        <v>0.23509868714834337</v>
+      </c>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
@@ -4945,7 +5067,7 @@
         <v>-9.5569070373588194E-2</v>
       </c>
       <c r="I29" s="16">
-        <f t="shared" ref="I29:M31" si="17">+I11/E11-1</f>
+        <f t="shared" ref="I29:N31" si="17">+I11/E11-1</f>
         <v>-0.12753829711435694</v>
       </c>
       <c r="J29" s="16">
@@ -4964,7 +5086,10 @@
         <f t="shared" si="17"/>
         <v>-0.10330747243772975</v>
       </c>
-      <c r="N29" s="16"/>
+      <c r="N29" s="16">
+        <f t="shared" si="17"/>
+        <v>-6.9279493269992054E-2</v>
+      </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="16" t="e">
@@ -4988,10 +5113,13 @@
         <v>-5.9553174994714242E-2</v>
       </c>
       <c r="V29" s="16">
-        <f t="shared" ref="V29:V31" si="18">+V11/U11-1</f>
+        <f t="shared" ref="V29:W31" si="18">+V11/U11-1</f>
         <v>-0.10289268585131905</v>
       </c>
-      <c r="W29" s="3"/>
+      <c r="W29" s="16">
+        <f t="shared" si="18"/>
+        <v>-0.10208002673126704</v>
+      </c>
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
@@ -5169,7 +5297,10 @@
         <f t="shared" si="17"/>
         <v>-1</v>
       </c>
-      <c r="N30" s="16"/>
+      <c r="N30" s="16">
+        <f t="shared" si="17"/>
+        <v>-1</v>
+      </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="16" t="e">
@@ -5196,7 +5327,10 @@
         <f t="shared" si="18"/>
         <v>-0.10931677018633545</v>
       </c>
-      <c r="W30" s="3"/>
+      <c r="W30" s="16">
+        <f t="shared" si="18"/>
+        <v>-0.93212459321245933</v>
+      </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
@@ -5374,7 +5508,10 @@
         <f t="shared" si="17"/>
         <v>0.21204089360090883</v>
       </c>
-      <c r="N31" s="17"/>
+      <c r="N31" s="17">
+        <f t="shared" si="17"/>
+        <v>8.9020427112348921E-2</v>
+      </c>
       <c r="O31" s="15"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="17" t="e">
@@ -5401,7 +5538,10 @@
         <f t="shared" si="18"/>
         <v>5.0890394531718508E-2</v>
       </c>
-      <c r="W31" s="3"/>
+      <c r="W31" s="17">
+        <f t="shared" si="18"/>
+        <v>0.14171195458370778</v>
+      </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
@@ -5591,7 +5731,10 @@
         <f>+M15/M13</f>
         <v>0.76877017598667086</v>
       </c>
-      <c r="N32" s="16"/>
+      <c r="N32" s="16">
+        <f>+N15/N13</f>
+        <v>0.83320899499094103</v>
+      </c>
       <c r="O32" s="3"/>
       <c r="P32" s="16" t="e">
         <f t="shared" ref="P32:V32" si="20">+P15/P13</f>
@@ -5621,7 +5764,10 @@
         <f t="shared" si="20"/>
         <v>0.75440398248391738</v>
       </c>
-      <c r="W32" s="3"/>
+      <c r="W32" s="16">
+        <f t="shared" ref="W32" si="21">+W15/W13</f>
+        <v>0.77821643637090532</v>
+      </c>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
@@ -5768,27 +5914,27 @@
         <v>42</v>
       </c>
       <c r="C33" s="16">
-        <f t="shared" ref="C33:H33" si="21">+C17/C13</f>
+        <f t="shared" ref="C33:H33" si="22">+C17/C13</f>
         <v>0.16732751784298178</v>
       </c>
       <c r="D33" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.21472775245862324</v>
       </c>
       <c r="E33" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.13781705342687536</v>
       </c>
       <c r="F33" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.14769656212682997</v>
       </c>
       <c r="G33" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.1671641791044777</v>
       </c>
       <c r="H33" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.22446934499407861</v>
       </c>
       <c r="I33" s="16">
@@ -5811,37 +5957,43 @@
         <f>+M17/M13</f>
         <v>0.22258669165885661</v>
       </c>
-      <c r="N33" s="16"/>
+      <c r="N33" s="16">
+        <f>+N17/N13</f>
+        <v>0.23569220931471779</v>
+      </c>
       <c r="O33" s="3"/>
       <c r="P33" s="16" t="e">
-        <f t="shared" ref="P33:V33" si="22">+P17/P13</f>
+        <f t="shared" ref="P33:V33" si="23">+P17/P13</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q33" s="16" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R33" s="16" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S33" s="16" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T33" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.17601225059676615</v>
       </c>
       <c r="U33" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.17089878882359993</v>
       </c>
       <c r="V33" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.9195230148202035E-2</v>
       </c>
-      <c r="W33" s="3"/>
+      <c r="W33" s="16">
+        <f t="shared" ref="W33" si="24">+W17/W13</f>
+        <v>0.23917443342245318</v>
+      </c>
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
@@ -5988,27 +6140,27 @@
         <v>43</v>
       </c>
       <c r="C34" s="16">
-        <f t="shared" ref="C34:H34" si="23">+C21/C20</f>
+        <f t="shared" ref="C34:H34" si="25">+C21/C20</f>
         <v>0.1823899371069182</v>
       </c>
       <c r="D34" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.20044653932026785</v>
       </c>
       <c r="E34" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.17758112094395276</v>
       </c>
       <c r="F34" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.20667330677290929</v>
       </c>
       <c r="G34" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.1732388125830748</v>
       </c>
       <c r="H34" s="16">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.10107153200115836</v>
       </c>
       <c r="I34" s="16">
@@ -6031,37 +6183,43 @@
         <f>+M21/M20</f>
         <v>0.1735576923076923</v>
       </c>
-      <c r="N34" s="16"/>
+      <c r="N34" s="16">
+        <f>+N21/N20</f>
+        <v>0.18889925373134347</v>
+      </c>
       <c r="O34" s="3"/>
       <c r="P34" s="16" t="e">
-        <f t="shared" ref="P34:V34" si="24">+P21/P20</f>
+        <f t="shared" ref="P34:V34" si="26">+P21/P20</f>
         <v>#DIV/0!</v>
       </c>
       <c r="Q34" s="16" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R34" s="16" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="S34" s="16" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T34" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.1811740005248885</v>
       </c>
       <c r="U34" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.19359620515861253</v>
       </c>
       <c r="V34" s="16">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.15224433132808884</v>
       </c>
-      <c r="W34" s="3"/>
+      <c r="W34" s="16">
+        <f t="shared" ref="W34" si="27">+W21/W20</f>
+        <v>0.17892077824357736</v>
+      </c>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
